--- a/data/gravel/State 4130 All-Road 2025.xlsx
+++ b/data/gravel/State 4130 All-Road 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A347B4-FC11-BB4B-B431-2D7F12358D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5800A7-22D3-C145-8F08-EF03EAB26CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2680" yWindow="500" windowWidth="25020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
   <si>
     <t>brand</t>
   </si>
@@ -402,6 +402,9 @@
   </si>
   <si>
     <t>a8:f37</t>
+  </si>
+  <si>
+    <t>threaded</t>
   </si>
 </sst>
 </file>
@@ -1540,6 +1543,9 @@
       <c r="A54" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="B54" s="1" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">

--- a/data/gravel/State 4130 All-Road 2025.xlsx
+++ b/data/gravel/State 4130 All-Road 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5800A7-22D3-C145-8F08-EF03EAB26CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFAE793-2F37-2E40-A17D-8AB8BA54F47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2680" yWindow="500" windowWidth="25020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -405,6 +405,9 @@
   </si>
   <si>
     <t>threaded</t>
+  </si>
+  <si>
+    <t>https://www.statebicycle.com/cdn/shop/files/4130All-Road-DromendaryTan_12Speed_UDH_-16.jpg?v=1737954578</t>
   </si>
 </sst>
 </file>
@@ -811,6 +814,9 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>124</v>
+      </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>

--- a/data/gravel/State 4130 All-Road 2025.xlsx
+++ b/data/gravel/State 4130 All-Road 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFAE793-2F37-2E40-A17D-8AB8BA54F47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A825E795-62DF-C145-9A8F-4991B176F434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2680" yWindow="500" windowWidth="25020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t>brand</t>
   </si>
@@ -260,9 +260,6 @@
     <t>rider_max_spec</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>Reach</t>
   </si>
   <si>
@@ -408,6 +405,15 @@
   </si>
   <si>
     <t>https://www.statebicycle.com/cdn/shop/files/4130All-Road-DromendaryTan_12Speed_UDH_-16.jpg?v=1737954578</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Phoenix, Arizona, USA</t>
   </si>
 </sst>
 </file>
@@ -766,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -778,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -786,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -810,12 +816,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -832,7 +838,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -849,27 +855,27 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9" s="1">
         <v>496</v>
@@ -889,7 +895,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" s="1">
         <v>75</v>
@@ -906,10 +912,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" s="1">
         <v>268</v>
@@ -929,7 +935,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C12" s="1">
         <v>450</v>
@@ -946,42 +952,42 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -989,7 +995,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C15" s="1">
         <v>165</v>
@@ -1009,7 +1015,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C16" s="1">
         <v>510</v>
@@ -1029,7 +1035,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C17" s="1">
         <v>405</v>
@@ -1049,7 +1055,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1069,7 +1075,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C19" s="1">
         <v>70.5</v>
@@ -1089,7 +1095,7 @@
         <v>9</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C20" s="1">
         <v>125</v>
@@ -1109,7 +1115,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C21" s="1">
         <v>359.8</v>
@@ -1129,7 +1135,7 @@
         <v>7</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C22" s="1">
         <v>430</v>
@@ -1149,7 +1155,7 @@
         <v>10</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C23" s="1">
         <v>75</v>
@@ -1169,7 +1175,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C24" s="1">
         <v>560.70000000000005</v>
@@ -1189,7 +1195,7 @@
         <v>15</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C25" s="1">
         <f>VALUE(LEFT(G25,3))</f>
@@ -1208,16 +1214,16 @@
         <v>827</v>
       </c>
       <c r="G25" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
@@ -1225,7 +1231,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C26" s="1">
         <v>997.1</v>
@@ -1458,7 +1464,7 @@
         <v>68</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
@@ -1474,7 +1480,7 @@
         <v>31</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
@@ -1498,7 +1504,7 @@
         <v>55</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
@@ -1550,7 +1556,7 @@
         <v>42</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -1601,7 +1607,7 @@
         <v>51</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -1680,7 +1686,15 @@
         <v>65</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>75</v>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/State 4130 All-Road 2025.xlsx
+++ b/data/gravel/State 4130 All-Road 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A825E795-62DF-C145-9A8F-4991B176F434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40A9F00-9411-3D44-A53B-BBD547CE7AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2680" yWindow="500" windowWidth="25020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="340" yWindow="500" windowWidth="26520" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -254,12 +254,6 @@
     <t>trail</t>
   </si>
   <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
-  </si>
-  <si>
     <t>Reach</t>
   </si>
   <si>
@@ -368,9 +362,6 @@
     <t>Wheel Base</t>
   </si>
   <si>
-    <t>:</t>
-  </si>
-  <si>
     <t>State</t>
   </si>
   <si>
@@ -398,9 +389,6 @@
     <t>55 frame, 45 stock fork, 50 carbon fork, 58 monster fork</t>
   </si>
   <si>
-    <t>a8:f37</t>
-  </si>
-  <si>
     <t>threaded</t>
   </si>
   <si>
@@ -414,6 +402,12 @@
   </si>
   <si>
     <t>Phoenix, Arizona, USA</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>a8:f35</t>
   </si>
 </sst>
 </file>
@@ -772,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -784,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -792,7 +786,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -816,12 +810,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -838,7 +832,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -855,27 +849,27 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C9" s="1">
         <v>496</v>
@@ -895,7 +889,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C10" s="1">
         <v>75</v>
@@ -912,10 +906,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C11" s="1">
         <v>268</v>
@@ -935,7 +929,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C12" s="1">
         <v>450</v>
@@ -952,42 +946,42 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -995,7 +989,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C15" s="1">
         <v>165</v>
@@ -1015,7 +1009,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C16" s="1">
         <v>510</v>
@@ -1035,7 +1029,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C17" s="1">
         <v>405</v>
@@ -1055,7 +1049,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1075,7 +1069,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C19" s="1">
         <v>70.5</v>
@@ -1095,7 +1089,7 @@
         <v>9</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C20" s="1">
         <v>125</v>
@@ -1115,7 +1109,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C21" s="1">
         <v>359.8</v>
@@ -1135,7 +1129,7 @@
         <v>7</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C22" s="1">
         <v>430</v>
@@ -1155,7 +1149,7 @@
         <v>10</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C23" s="1">
         <v>75</v>
@@ -1175,7 +1169,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C24" s="1">
         <v>560.70000000000005</v>
@@ -1195,7 +1189,7 @@
         <v>15</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C25" s="1">
         <f>VALUE(LEFT(G25,3))</f>
@@ -1214,16 +1208,16 @@
         <v>827</v>
       </c>
       <c r="G25" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
@@ -1231,7 +1225,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C26" s="1">
         <v>997.1</v>
@@ -1332,20 +1326,20 @@
         <v>27</v>
       </c>
       <c r="C34" s="1">
-        <f>C36</f>
+        <f>C36*2.54</f>
         <v>154.94</v>
       </c>
       <c r="D34" s="1">
-        <f>AVERAGE(D36,C37)</f>
-        <v>166.37</v>
+        <f t="shared" ref="D34:F35" si="1">D36*2.54</f>
+        <v>165.1</v>
       </c>
       <c r="E34" s="1">
-        <f t="shared" ref="E34:F34" si="1">AVERAGE(E36,D37)</f>
-        <v>176.53</v>
+        <f t="shared" si="1"/>
+        <v>175.26</v>
       </c>
       <c r="F34" s="1">
         <f t="shared" si="1"/>
-        <v>186.69</v>
+        <v>185.42000000000002</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
@@ -1353,105 +1347,79 @@
         <v>28</v>
       </c>
       <c r="C35" s="1">
-        <f>D34</f>
-        <v>166.37</v>
+        <f>C37*2.54</f>
+        <v>167.64000000000001</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" ref="D35:E35" si="2">E34</f>
-        <v>176.53</v>
+        <f t="shared" si="1"/>
+        <v>177.8</v>
       </c>
       <c r="E35" s="1">
-        <f t="shared" si="2"/>
-        <v>186.69</v>
+        <f t="shared" si="1"/>
+        <v>187.96</v>
       </c>
       <c r="F35" s="1">
-        <f>F37</f>
+        <f t="shared" si="1"/>
         <v>193.04</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="C36" s="1">
+        <v>61</v>
+      </c>
+      <c r="D36" s="1">
+        <v>65</v>
+      </c>
+      <c r="E36" s="1">
+        <v>69</v>
+      </c>
+      <c r="F36" s="1">
         <v>73</v>
-      </c>
-      <c r="C36" s="1">
-        <f>C38*2.54</f>
-        <v>154.94</v>
-      </c>
-      <c r="D36" s="1">
-        <f t="shared" ref="D36:F37" si="3">D38*2.54</f>
-        <v>165.1</v>
-      </c>
-      <c r="E36" s="1">
-        <f t="shared" si="3"/>
-        <v>175.26</v>
-      </c>
-      <c r="F36" s="1">
-        <f t="shared" si="3"/>
-        <v>185.42000000000002</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="1">
+        <v>66</v>
+      </c>
+      <c r="D37" s="1">
+        <v>70</v>
+      </c>
+      <c r="E37" s="1">
         <v>74</v>
       </c>
-      <c r="C37" s="1">
-        <f>C39*2.54</f>
-        <v>167.64000000000001</v>
-      </c>
-      <c r="D37" s="1">
-        <f t="shared" si="3"/>
-        <v>177.8</v>
-      </c>
-      <c r="E37" s="1">
-        <f t="shared" si="3"/>
-        <v>187.96</v>
-      </c>
       <c r="F37" s="1">
-        <f t="shared" si="3"/>
-        <v>193.04</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C38" s="1">
-        <v>61</v>
-      </c>
-      <c r="D38" s="1">
-        <v>65</v>
-      </c>
-      <c r="E38" s="1">
-        <v>69</v>
-      </c>
-      <c r="F38" s="1">
-        <v>73</v>
+      <c r="A38" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" s="1">
-        <v>66</v>
-      </c>
-      <c r="D39" s="1">
-        <v>70</v>
-      </c>
-      <c r="E39" s="1">
-        <v>74</v>
-      </c>
-      <c r="F39" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -1461,240 +1429,224 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>116</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>71</v>
+        <v>34</v>
+      </c>
+      <c r="B44" s="1">
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="B45" s="6">
+        <v>2.25</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="1">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" s="6">
-        <v>2.25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="B50" s="1">
+        <v>142</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="B51" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="1">
-        <v>142</v>
+        <v>42</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="1">
-        <v>100</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>122</v>
+        <v>44</v>
+      </c>
+      <c r="B54" s="1">
+        <v>27.2</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="1">
-        <v>27.2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="B72" s="1">
+        <v>499</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="B73" s="1">
+        <v>999</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B74" s="1">
-        <v>499</v>
+        <v>64</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B75" s="1">
-        <v>999</v>
+        <v>65</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/State 4130 All-Road 2025.xlsx
+++ b/data/gravel/State 4130 All-Road 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40A9F00-9411-3D44-A53B-BBD547CE7AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE72352-312A-874C-A67D-460FD5201FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="340" yWindow="500" windowWidth="26520" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <si>
     <t>brand</t>
   </si>
@@ -408,6 +408,24 @@
   </si>
   <si>
     <t>a8:f35</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -766,7 +784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1505,147 +1523,177 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="1">
-        <v>27.2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>45</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>46</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>47</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B60" s="1">
+        <v>27.2</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B72" s="1">
-        <v>499</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B73" s="1">
-        <v>999</v>
+        <v>57</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B78" s="1">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B79" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>122</v>
       </c>
     </row>

--- a/data/gravel/State 4130 All-Road 2025.xlsx
+++ b/data/gravel/State 4130 All-Road 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE72352-312A-874C-A67D-460FD5201FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39980CF-64DC-8E4C-8311-B2B01243C051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="340" yWindow="500" windowWidth="26520" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16260" yWindow="1180" windowWidth="26520" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="131">
   <si>
     <t>brand</t>
   </si>
@@ -1629,35 +1629,56 @@
       <c r="A71" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="B71" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="B72" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="B73" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="B74" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="B75" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="B76" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>61</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
